--- a/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
+++ b/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Параметры" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Документы и риски" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Источники" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Чек-лист до заказа" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8380,4 +8381,288 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Что сделать до заказа (прямой импорт Китай → РФ, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Отмечайте выполнение в колонке «Статус». Порядок шагов — рекомендуемый.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Что сделать</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1. Схема</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Выбрать схему: (а) свой контракт + свой валютный счёт + брокер — дешевле, всё под контролем; (б) ВЭД-агент «под ключ» — вы платите рублями агенту, он сам контрактует и оплачивает Китай (+3–7% к стоимости, быстрее старт); (в) купить у российского импортёра. Для регулярных закупок — схема (а).</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>1. Схема</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Не брать товар, растаможенный в Казахстане/Киргизии/Армении: с 01.06.2026 такой ввоз идёт через СПОТ (уведомление ФНС, QR-код, обеспечительный платёж НДС до ввоза). Прямой ввоз из Китая с растаможкой в РФ и транзит через Казахстан под таможенным транзитом под СПОТ не подпадают.</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2. Поставщик</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Проверить поставщика: бизнес-лицензия (qcc.com / gsxt.gov.cn), завод или трейдер, опыт работы с РФ, готовность отгружать в РФ. По Vileda — подтверждение легальности товарного знака; по Genie/JLG/Haulotte — санкционный риск, рассмотреть Dingli/Sinoboom/LGMG/XCMG.</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2. Поставщик</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Получить спецификации по каждой позиции: состав/материал, вес нетто и брутто, габариты, фото, паспорта, мощность/напряжение, тип АКБ, MSDS на химию и аккумуляторы. Без веса нетто не посчитать пошлину на микрофибру.</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2. Поставщик</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Заранее спросить: в каком банке счёт поставщика и принимает ли он платежи из РФ в юанях (CNY). Крупные госбанки КНР часто отклоняют; региональные банки и счета в спецрайонах — лучше.</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>3. Брокер</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Выбрать таможенного представителя из реестра ФТС, согласовать коды ТН ВЭД и ставки по этой таблице ДО отгрузки, стоимость (ДТ + доп. коды), пункт оформления (ближе к вашему складу).</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>3. Брокер</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Спорные коды — предварительное решение ФТС (до 90 дней) или письменное подтверждение брокера.</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>4. Документы</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Оформить сертификаты/декларации ЕАЭС ДО прибытия товара (заявитель — ваше юрлицо). Для ТР ТС 004/020 нужны протоколы испытаний — возможно, образцы. Отказные письма на инвентарь Vileda. Проверить «Честный знак» для кода 6307.</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>4. Документы</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Маркировка на упаковке: знак EAC (для сертифицированных), информация на русском языке (наименование, изготовитель, импортёр) — передать макет поставщику до производства.</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>5. Контракт</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Внешнеторговый контракт в юанях (CNY) — расчёты в USD/EUR с Китаем практически не проходят. Двуязычный (RU/EN или RU/CN).</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>5. Контракт</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>В контракте: спецификации-приложения (наименование, кол-во, цена, вес), Инкотермс 2020 (FOB порт / EXW / DAP граница), условия оплаты (напр. 30% аванс / 70% после отгрузки по копии коносамента/CMR), срок поставки, требования к упаковке и маркировке, рекламации, форс-мажор включая санкции и отказ банков, арбитраж (МКАС ТПП РФ или CIETAC).</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>5. Контракт</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Оговорка о возможности оплаты третьим лицом (платёжным агентом) — на случай, если прямой платёж не пройдёт. Без неё оплата через агента — нарушение валютного законодательства.</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>6. Банк</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Открыть валютный счёт в CNY (основной + резервный банк). Сравнивать итоговую стоимость: комиссия за перевод + спред конвертации RUB→CNY (обычно основная часть затрат) + комиссии банков-корреспондентов; срок зачисления; долю возвратов платежей.</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>6. Банк</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Контракт ≥ 3 млн ₽ — поставить на учёт в банке (УНК) до первого платежа (Инструкция ЦБ № 181-И). Указать ожидаемые сроки поставки по авансу.</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>6. Банк</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Аванс: если товар не ввезён в срок по контракту — обязанность вернуть аванс (ст. 19 173-ФЗ), иначе штраф. Сроки ставьте с запасом.</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>7. Деньги на таможню</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Открыть личный кабинет участника ВЭД ФТС, пополнить единый лицевой счёт (ЕЛС) в рублях под пошлину + НДС 22% + сбор — платится ДО выпуска. НДС вернётся вычетом (ОСНО) только в следующем квартале — заложить в кассовый разрыв.</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>8. Логистика</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Выбрать маршрут (авто через Забайкальск/Благовещенск, ж/д, море через Владивосток, транзит через Казахстан), страхование груза, опасные грузы (химия, Li-ion) — отдельные условия.</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>9. После ввоза</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Подъёмники: ЭПСМ, регистрация в Гостехнадзоре, утильсбор. Бухучёт импорта, вычет НДС по ДТ и платёжке.</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
+++ b/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
@@ -8389,7 +8389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8652,15 +8652,93 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>4. Документы</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Маркировка «Честный знак»: тряпки, мопы, щётки пока только в добровольном эксперименте (до 28.02.2027) — сейчас для ввоза не нужна. Перед каждой поставкой в 2027 г. проверить, не ввели ли обязательную маркировку этих кодов.</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>4. Документы</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Инвентарь под аренду = собственные нужды, не перепродажа: в контракте и заявке брокеру указать цель ввоза «для собственных нужд (сдача в аренду), не для реализации»; учитывать как своё имущество, а не товар. Если часть будет продаваться — заранее зарегистрироваться в «Честном знаке» (бесплатно, нужна ЭЦП).</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>5. Контракт</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>До заказа проверить налоговый режим: ОСНО или УСН с НДС 22% — ввозной НДС к вычету; УСН без НДС или с НДС 5%/7% — вычета нет, НДС идёт в стоимость (с 2026 г. НДС на УСН платят при доходе &gt; 20 млн ₽/год).</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>9. После ввоза</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Подъёмники: ЭПСМ, регистрация в Гостехнадзоре, утильсбор. Бухучёт импорта, вычет НДС по ДТ и платёжке.</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Подъёмники: ЭПСМ, регистрация в Гостехнадзоре, утильсбор. Бухучёт импорта.</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>9. После ввоза</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Вычет ввозного НДС (ст. 171 п. 2, 172 НК): в квартале, когда товар выпущен, принят к учёту и НДС уплачен (ДТ + платёжка на ЕЛС ФТС + отчёт о расходовании из ЛК участника ВЭД). Пример: выпуск в ноябре 2026 → декларация за IV кв. до 25.01.2027.</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>9. После ввоза</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Инвентарь (МПЗ): вычет можно перенести в пределах 3 лет с даты принятия к учёту. Подъёмники (ОС): вычет после принятия к учёту, безопаснее — после ввода в эксплуатацию и целиком в одном квартале.</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>9. После ввоза</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Кассовый разрыв: если вычет больше НДС с аренды — возмещение после камеральной проверки (до 2 мес.). Деньги вернутся примерно через 3–5 месяцев после уплаты на таможне.</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
+++ b/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
@@ -8389,7 +8389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8522,12 +8522,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>4. Документы</t>
+          <t>3. Брокер</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Оформить сертификаты/декларации ЕАЭС ДО прибытия товара (заявитель — ваше юрлицо). Для ТР ТС 004/020 нужны протоколы испытаний — возможно, образцы. Отказные письма на инвентарь Vileda. Проверить «Честный знак» для кода 6307.</t>
+          <t>Проверка брокера: есть в реестре таможенных представителей ФТС (customs.gov.ru), работает 5+ лет, есть опыт с Китаем и с оборудованием/электротехникой, обеспечение и страхование ответственности, офис на вашем посту оформления. В договоре — ответственность брокера за ошибки в кодах и штрафы по его вине.</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr"/>
@@ -8535,12 +8535,12 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>4. Документы</t>
+          <t>3. Брокер</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Маркировка на упаковке: знак EAC (для сертифицированных), информация на русском языке (наименование, изготовитель, импортёр) — передать макет поставщику до производства.</t>
+          <t>Спросить брокера: сколько ДТ в месяц по Китаю, кто подбирает коды, помогает ли с сертификацией и маркировкой, как считает КТС, берёт ли платежи через свой ЕЛС. Настораживает: «растаможка под ключ по весу/кубам», «белая» цена ниже расчёта, оформление на чужую фирму.</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr"/>
@@ -8548,12 +8548,12 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>5. Контракт</t>
+          <t>4. Документы</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Внешнеторговый контракт в юанях (CNY) — расчёты в USD/EUR с Китаем практически не проходят. Двуязычный (RU/EN или RU/CN).</t>
+          <t>Оформить сертификаты/декларации ЕАЭС ДО прибытия товара (заявитель — ваше юрлицо). Для ТР ТС 004/020 нужны протоколы испытаний — возможно, образцы. Отказные письма на инвентарь Vileda. Проверить «Честный знак» для кода 6307.</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr"/>
@@ -8561,12 +8561,12 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>5. Контракт</t>
+          <t>4. Документы</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>В контракте: спецификации-приложения (наименование, кол-во, цена, вес), Инкотермс 2020 (FOB порт / EXW / DAP граница), условия оплаты (напр. 30% аванс / 70% после отгрузки по копии коносамента/CMR), срок поставки, требования к упаковке и маркировке, рекламации, форс-мажор включая санкции и отказ банков, арбитраж (МКАС ТПП РФ или CIETAC).</t>
+          <t>Маркировка на упаковке: знак EAC (для сертифицированных), информация на русском языке (наименование, изготовитель, импортёр) — передать макет поставщику до производства.</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr"/>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Оговорка о возможности оплаты третьим лицом (платёжным агентом) — на случай, если прямой платёж не пройдёт. Без неё оплата через агента — нарушение валютного законодательства.</t>
+          <t>Внешнеторговый контракт в юанях (CNY) — расчёты в USD/EUR с Китаем практически не проходят. Двуязычный (RU/EN или RU/CN).</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr"/>
@@ -8587,12 +8587,12 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>6. Банк</t>
+          <t>5. Контракт</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Открыть валютный счёт в CNY (основной + резервный банк). Сравнивать итоговую стоимость: комиссия за перевод + спред конвертации RUB→CNY (обычно основная часть затрат) + комиссии банков-корреспондентов; срок зачисления; долю возвратов платежей.</t>
+          <t>В контракте: спецификации-приложения (наименование, кол-во, цена, вес), Инкотермс 2020 (FOB порт / EXW / DAP граница), условия оплаты (напр. 30% аванс / 70% после отгрузки по копии коносамента/CMR), срок поставки, требования к упаковке и маркировке, рекламации, форс-мажор включая санкции и отказ банков, арбитраж (МКАС ТПП РФ или CIETAC).</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr"/>
@@ -8600,12 +8600,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>6. Банк</t>
+          <t>5. Контракт</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Контракт ≥ 3 млн ₽ — поставить на учёт в банке (УНК) до первого платежа (Инструкция ЦБ № 181-И). Указать ожидаемые сроки поставки по авансу.</t>
+          <t>Оговорка о возможности оплаты третьим лицом (платёжным агентом) — на случай, если прямой платёж не пройдёт. Без неё оплата через агента — нарушение валютного законодательства.</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr"/>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Аванс: если товар не ввезён в срок по контракту — обязанность вернуть аванс (ст. 19 173-ФЗ), иначе штраф. Сроки ставьте с запасом.</t>
+          <t>Открыть валютный счёт в CNY (основной + резервный банк). Сравнивать итоговую стоимость: комиссия за перевод + спред конвертации RUB→CNY (обычно основная часть затрат) + комиссии банков-корреспондентов; срок зачисления; долю возвратов платежей.</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr"/>
@@ -8626,12 +8626,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>7. Деньги на таможню</t>
+          <t>6. Банк</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Открыть личный кабинет участника ВЭД ФТС, пополнить единый лицевой счёт (ЕЛС) в рублях под пошлину + НДС 22% + сбор — платится ДО выпуска. НДС вернётся вычетом (ОСНО) только в следующем квартале — заложить в кассовый разрыв.</t>
+          <t>Контракт ≥ 3 млн ₽ — поставить на учёт в банке (УНК) до первого платежа (Инструкция ЦБ № 181-И). Указать ожидаемые сроки поставки по авансу.</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr"/>
@@ -8639,12 +8639,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>8. Логистика</t>
+          <t>6. Банк</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Выбрать маршрут (авто через Забайкальск/Благовещенск, ж/д, море через Владивосток, транзит через Казахстан), страхование груза, опасные грузы (химия, Li-ion) — отдельные условия.</t>
+          <t>Аванс: если товар не ввезён в срок по контракту — обязанность вернуть аванс (ст. 19 173-ФЗ), иначе штраф. Сроки ставьте с запасом.</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr"/>
@@ -8652,12 +8652,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>4. Документы</t>
+          <t>7. Деньги на таможню</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Маркировка «Честный знак»: тряпки, мопы, щётки пока только в добровольном эксперименте (до 28.02.2027) — сейчас для ввоза не нужна. Перед каждой поставкой в 2027 г. проверить, не ввели ли обязательную маркировку этих кодов.</t>
+          <t>Открыть личный кабинет участника ВЭД ФТС, пополнить единый лицевой счёт (ЕЛС) в рублях под пошлину + НДС 22% + сбор — платится ДО выпуска. НДС вернётся вычетом (ОСНО) только в следующем квартале — заложить в кассовый разрыв.</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr"/>
@@ -8665,12 +8665,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>4. Документы</t>
+          <t>8. Логистика</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Инвентарь под аренду = собственные нужды, не перепродажа: в контракте и заявке брокеру указать цель ввоза «для собственных нужд (сдача в аренду), не для реализации»; учитывать как своё имущество, а не товар. Если часть будет продаваться — заранее зарегистрироваться в «Честном знаке» (бесплатно, нужна ЭЦП).</t>
+          <t>Выбрать маршрут (авто через Забайкальск/Благовещенск, ж/д, море через Владивосток, транзит через Казахстан), страхование груза, опасные грузы (химия, Li-ion) — отдельные условия.</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr"/>
@@ -8678,12 +8678,12 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>5. Контракт</t>
+          <t>4. Документы</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>До заказа проверить налоговый режим: ОСНО или УСН с НДС 22% — ввозной НДС к вычету; УСН без НДС или с НДС 5%/7% — вычета нет, НДС идёт в стоимость (с 2026 г. НДС на УСН платят при доходе &gt; 20 млн ₽/год).</t>
+          <t>Химию закупать в профессиональной таре (канистры 5–20 л, код 3402 90 900 0) — под маркировку не попадает. Бытовая химия в розничной фасовке (3401, 3402 50 000 0, 3405 40) при самостоятельном ввозе — маркировка импортёром до ввоза.</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr"/>
@@ -8691,12 +8691,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>9. После ввоза</t>
+          <t>4. Документы</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Подъёмники: ЭПСМ, регистрация в Гостехнадзоре, утильсбор. Бухучёт импорта.</t>
+          <t>Пылесосы, мойки, аккумуляторный инструмент, Windomatic: обязательная маркировка радиоэлектроники/бытовой техники (ПП № 1954 от 28.11.2025), с 01.12.2026 немаркированный оборот запрещён. Сдача в аренду от обязанности импортёра не освобождает — брокер сверяет коды с приложением к ПП № 1954 до отгрузки; при необходимости — регистрация в «Честном знаке» и заказ кодов до ввоза.</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr"/>
@@ -8704,12 +8704,12 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>9. После ввоза</t>
+          <t>4. Документы</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Вычет ввозного НДС (ст. 171 п. 2, 172 НК): в квартале, когда товар выпущен, принят к учёту и НДС уплачен (ДТ + платёжка на ЕЛС ФТС + отчёт о расходовании из ЛК участника ВЭД). Пример: выпуск в ноябре 2026 → декларация за IV кв. до 25.01.2027.</t>
+          <t>Маркировка «Честный знак»: тряпки, мопы, щётки пока только в добровольном эксперименте (до 28.02.2027) — сейчас для ввоза не нужна. Перед каждой поставкой в 2027 г. проверить, не ввели ли обязательную маркировку этих кодов.</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr"/>
@@ -8717,12 +8717,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>9. После ввоза</t>
+          <t>4. Документы</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Инвентарь (МПЗ): вычет можно перенести в пределах 3 лет с даты принятия к учёту. Подъёмники (ОС): вычет после принятия к учёту, безопаснее — после ввода в эксплуатацию и целиком в одном квартале.</t>
+          <t>Инвентарь под аренду = собственные нужды, не перепродажа: в контракте и заявке брокеру указать цель ввоза «для собственных нужд (сдача в аренду), не для реализации»; учитывать как своё имущество, а не товар. Если часть будет продаваться — заранее зарегистрироваться в «Честном знаке» (бесплатно, нужна ЭЦП).</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr"/>
@@ -8730,15 +8730,93 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
+          <t>5. Контракт</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>До заказа проверить налоговый режим: ОСНО или УСН с НДС 22% — ввозной НДС к вычету; УСН без НДС или с НДС 5%/7% — вычета нет, НДС идёт в стоимость (с 2026 г. НДС на УСН платят при доходе &gt; 20 млн ₽/год).</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
           <t>9. После ввоза</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Подъёмники: ЭПСМ, регистрация в Гостехнадзоре, утильсбор. Бухучёт импорта.</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>9. После ввоза</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Вычет ввозного НДС (ст. 171 п. 2, 172 НК): в квартале, когда товар выпущен, принят к учёту и НДС уплачен (ДТ + платёжка на ЕЛС ФТС + отчёт о расходовании из ЛК участника ВЭД). Пример: выпуск в ноябре 2026 → декларация за IV кв. до 25.01.2027.</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>9. После ввоза</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Инвентарь (МПЗ): вычет можно перенести в пределах 3 лет с даты принятия к учёту. Подъёмники (ОС): вычет после принятия к учёту, безопаснее — после ввода в эксплуатацию и целиком в одном квартале.</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>9. После ввоза</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Экологический сбор (ст. 24.5 ФЗ-89): за упаковку и за товары из перечня ПП РФ № 2414 от 29.12.2023 (в т. ч. текстиль, изделия из пластмасс, электрооборудование, АКБ). Вести учёт массы ввезённых товаров и упаковки по кодам ТН ВЭД и видам упаковки (картон, плёнка, пластик, дерево).</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>9. После ввоза</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Экосбор: до 15 апреля следующего года — отчётность в Росприроднадзор (масса товаров и упаковки) и уплата сбора. Ставка = базовая ставка × коэффициент (ПП РФ № 1041 от 01.08.2024) × масса × норматив утилизации. Альтернатива — договор с утилизатором из реестра (закрыть норматив), иногда дешевле. Запросить у поставщика вес упаковки по видам.</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>9. После ввоза</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Кассовый разрыв: если вычет больше НДС с аренды — возмещение после камеральной проверки (до 2 мес.). Деньги вернутся примерно через 3–5 месяцев после уплаты на таможне.</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr"/>
+      <c r="C34" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
+++ b/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Параметры" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Документы и риски" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Источники" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Чек-лист до заказа" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Экосбор" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Чек-лист до заказа" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,12 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.00;(#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%;;&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00;;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -121,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -189,6 +191,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8389,6 +8402,365 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Расчёт экологического сбора за год (импортёр, ст. 24.5 ФЗ-89)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Экосбор = MAX(0; масса, т × норматив утилизации − утилизировано самостоятельно, т) × базовая ставка, ₽/т × коэффициент сложности. Сдать расчёт и заплатить — до 15 апреля следующего года (импортёры — в центральный аппарат Росприроднадзора).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Ставки и коэффициенты возьмите из ПП РФ № 1041 от 01.08.2024 (ред. от 11.03.2026) по номеру группы, нормативы — из ПП РФ № 2414 от 29.12.2023. Ввоз «для собственных нужд» (аренда, услуги) от экосбора НЕ освобождает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Что</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Что сюда входит из закупки</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Масса за год, кг</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Норматив утилизации</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Утилизировано самостоятельно / по договору, кг</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Базовая ставка, ₽/т</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Коэффициент сложности</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Экосбор, ₽</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>Упаковка — бумага и картон</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Гофрокороба, картонные вкладыши, бумажные этикетки</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="13">
+        <f>MAX(0,C6/1000*D6-E6/1000)*F6*G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Норматив упаковки 2026 — 75% (2027 — 100%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>Упаковка — полимерная</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Плёнка, пакеты, стрейч, пузырчатая плёнка, пластиковые вкладыши</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="n"/>
+      <c r="D7" s="34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E7" s="33" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13">
+        <f>MAX(0,C7/1000*D7-E7/1000)*F7*G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>Упаковка — деревянная</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Паллеты, обрешётка (если остаются у вас)</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13">
+        <f>MAX(0,C8/1000*D8-E8/1000)*F8*G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Возвратные поддоны перевозчика — не ваши.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>Товары — текстиль</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Мопы, салфетки, тряпки (6307)</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="n"/>
+      <c r="D9" s="34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="33" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13">
+        <f>MAX(0,C9/1000*D9-E9/1000)*F9*G9</f>
+        <v/>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Норматив текстиля 2026 — 30%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>Товары — изделия из пластмасс</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Вёдра, прессы, держатели, таблички (3924, 3926)</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="n"/>
+      <c r="D10" s="34" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E10" s="33" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="13">
+        <f>MAX(0,C10/1000*D10-E10/1000)*F10*G10</f>
+        <v/>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Норматив сверить с ПП № 2414 по номеру группы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Товары — электрооборудование</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Пылесосы, мойки, аппараты, удлинители, инструмент, Windomatic</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="33" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="13">
+        <f>MAX(0,C11/1000*D11-E11/1000)*F11*G11</f>
+        <v/>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Проверить группу и норматив в ПП № 2414; подъёмники — проверить, входят ли в перечень.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Товары — аккумуляторы</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Li-ion АКБ инструмента, Windomatic, тяговые АКБ подъёмников</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="33" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13">
+        <f>MAX(0,C12/1000*D12-E12/1000)*F12*G12</f>
+        <v/>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Отдельная группа; учитывать массу АКБ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Товары — химия</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Моющие средства и тара от них (3402)</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="33" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="13">
+        <f>MAX(0,C13/1000*D13-E13/1000)*F13*G13</f>
+        <v/>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Проверить, входит ли группа; тара от химии — учитывать как упаковку.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="inlineStr">
+        <is>
+          <t>ИТОГО экосбор за год, ₽</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="37" t="n"/>
+      <c r="H14" s="20">
+        <f>SUM(H6:H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="37" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Где взять массы: вес нетто товаров — из ДТ/упаковочных листов; вес упаковки по видам — запросить у поставщика в спецификации к контракту.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Если сумма велика — сравните с договором с утилизатором из реестра Росприроднадзора (норматив закрывается актом утилизации, колонка E).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
+++ b/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
@@ -7952,7 +7952,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Цены в листах вводятся в этой валюте (для CNY поменяйте курс в B4 на курс юаня).</t>
+          <t>Цены — по инвойсу поставщика БЕЗ НДС (экспорт из КНР идёт по 0%, китайский НДС возмещают продавцу). Для CNY поменяйте курс в B4 на курс юаня.</t>
         </is>
       </c>
       <c r="E7" s="26" t="n">
@@ -8761,7 +8761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>В контракте: спецификации-приложения (наименование, кол-во, цена, вес), Инкотермс 2020 (FOB порт / EXW / DAP граница), условия оплаты (напр. 30% аванс / 70% после отгрузки по копии коносамента/CMR), срок поставки, требования к упаковке и маркировке, рекламации, форс-мажор включая санкции и отказ банков, арбитраж (МКАС ТПП РФ или CIETAC).</t>
+          <t>Инвойс — без НДС: цена с экспортным оформлением в КНР (экспортная декларация на поставщика). Цена «без экспортной декларации» — риск для таможенной стоимости и документов.</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr"/>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Оговорка о возможности оплаты третьим лицом (платёжным агентом) — на случай, если прямой платёж не пройдёт. Без неё оплата через агента — нарушение валютного законодательства.</t>
+          <t>Выбрать юрлицо-импортёра: ввозной НДС 22% платит любое юрлицо (и на УСН без НДС), но к вычету — только плательщик НДС по ставке 22% (ОСНО — «Аргумент ЭК», или УСН с НДС 22%). На УСН 5%/7% и без НДС ввозной НДС идёт в стоимость. Сам ввоз в доход для порогов 20 / 272,5 млн не входит, а выручка от аренды — входит.</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr"/>
@@ -8985,12 +8985,12 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>6. Банк</t>
+          <t>5. Контракт</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Открыть валютный счёт в CNY (основной + резервный банк). Сравнивать итоговую стоимость: комиссия за перевод + спред конвертации RUB→CNY (обычно основная часть затрат) + комиссии банков-корреспондентов; срок зачисления; долю возвратов платежей.</t>
+          <t>В контракте: спецификации-приложения (наименование, кол-во, цена, вес), Инкотермс 2020 (FOB порт / EXW / DAP граница), условия оплаты (напр. 30% аванс / 70% после отгрузки по копии коносамента/CMR), срок поставки, требования к упаковке и маркировке, рекламации, форс-мажор включая санкции и отказ банков, арбитраж (МКАС ТПП РФ или CIETAC).</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr"/>
@@ -8998,12 +8998,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>6. Банк</t>
+          <t>5. Контракт</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Контракт ≥ 3 млн ₽ — поставить на учёт в банке (УНК) до первого платежа (Инструкция ЦБ № 181-И). Указать ожидаемые сроки поставки по авансу.</t>
+          <t>Оговорка о возможности оплаты третьим лицом (платёжным агентом) — на случай, если прямой платёж не пройдёт. Без неё оплата через агента — нарушение валютного законодательства.</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr"/>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Аванс: если товар не ввезён в срок по контракту — обязанность вернуть аванс (ст. 19 173-ФЗ), иначе штраф. Сроки ставьте с запасом.</t>
+          <t>Открыть валютный счёт в CNY (основной + резервный банк). Сравнивать итоговую стоимость: комиссия за перевод + спред конвертации RUB→CNY (обычно основная часть затрат) + комиссии банков-корреспондентов; срок зачисления; долю возвратов платежей.</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr"/>
@@ -9024,12 +9024,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>7. Деньги на таможню</t>
+          <t>6. Банк</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Открыть личный кабинет участника ВЭД ФТС, пополнить единый лицевой счёт (ЕЛС) в рублях под пошлину + НДС 22% + сбор — платится ДО выпуска. НДС вернётся вычетом (ОСНО) только в следующем квартале — заложить в кассовый разрыв.</t>
+          <t>Контракт ≥ 3 млн ₽ — поставить на учёт в банке (УНК) до первого платежа (Инструкция ЦБ № 181-И). Указать ожидаемые сроки поставки по авансу.</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr"/>
@@ -9037,12 +9037,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>8. Логистика</t>
+          <t>6. Банк</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Выбрать маршрут (авто через Забайкальск/Благовещенск, ж/д, море через Владивосток, транзит через Казахстан), страхование груза, опасные грузы (химия, Li-ion) — отдельные условия.</t>
+          <t>Аванс: если товар не ввезён в срок по контракту — обязанность вернуть аванс (ст. 19 173-ФЗ), иначе штраф. Сроки ставьте с запасом.</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr"/>
@@ -9050,12 +9050,12 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>4. Документы</t>
+          <t>7. Деньги на таможню</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Химию закупать в профессиональной таре (канистры 5–20 л, код 3402 90 900 0) — под маркировку не попадает. Бытовая химия в розничной фасовке (3401, 3402 50 000 0, 3405 40) при самостоятельном ввозе — маркировка импортёром до ввоза.</t>
+          <t>Открыть личный кабинет участника ВЭД ФТС, пополнить единый лицевой счёт (ЕЛС) в рублях под пошлину + НДС 22% + сбор — платится ДО выпуска. НДС вернётся вычетом (ОСНО) только в следующем квартале — заложить в кассовый разрыв.</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr"/>
@@ -9063,12 +9063,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>4. Документы</t>
+          <t>8. Логистика</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Пылесосы, мойки, аккумуляторный инструмент, Windomatic: обязательная маркировка радиоэлектроники/бытовой техники (ПП № 1954 от 28.11.2025), с 01.12.2026 немаркированный оборот запрещён. Сдача в аренду от обязанности импортёра не освобождает — брокер сверяет коды с приложением к ПП № 1954 до отгрузки; при необходимости — регистрация в «Честном знаке» и заказ кодов до ввоза.</t>
+          <t>Выбрать маршрут (авто через Забайкальск/Благовещенск, ж/д, море через Владивосток, транзит через Казахстан), страхование груза, опасные грузы (химия, Li-ion) — отдельные условия.</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr"/>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Маркировка «Честный знак»: тряпки, мопы, щётки пока только в добровольном эксперименте (до 28.02.2027) — сейчас для ввоза не нужна. Перед каждой поставкой в 2027 г. проверить, не ввели ли обязательную маркировку этих кодов.</t>
+          <t>Химию закупать в профессиональной таре (канистры 5–20 л, код 3402 90 900 0) — под маркировку не попадает. Бытовая химия в розничной фасовке (3401, 3402 50 000 0, 3405 40) при самостоятельном ввозе — маркировка импортёром до ввоза.</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr"/>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Инвентарь под аренду = собственные нужды, не перепродажа: в контракте и заявке брокеру указать цель ввоза «для собственных нужд (сдача в аренду), не для реализации»; учитывать как своё имущество, а не товар. Если часть будет продаваться — заранее зарегистрироваться в «Честном знаке» (бесплатно, нужна ЭЦП).</t>
+          <t>Пылесосы, мойки, аккумуляторный инструмент, Windomatic: обязательная маркировка радиоэлектроники/бытовой техники (ПП № 1954 от 28.11.2025), с 01.12.2026 немаркированный оборот запрещён. Сдача в аренду от обязанности импортёра не освобождает — брокер сверяет коды с приложением к ПП № 1954 до отгрузки; при необходимости — регистрация в «Честном знаке» и заказ кодов до ввоза.</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr"/>
@@ -9102,12 +9102,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>5. Контракт</t>
+          <t>4. Документы</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>До заказа проверить налоговый режим: ОСНО или УСН с НДС 22% — ввозной НДС к вычету; УСН без НДС или с НДС 5%/7% — вычета нет, НДС идёт в стоимость (с 2026 г. НДС на УСН платят при доходе &gt; 20 млн ₽/год).</t>
+          <t>Маркировка «Честный знак»: тряпки, мопы, щётки пока только в добровольном эксперименте (до 28.02.2027) — сейчас для ввоза не нужна. Перед каждой поставкой в 2027 г. проверить, не ввели ли обязательную маркировку этих кодов.</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr"/>
@@ -9115,12 +9115,12 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>9. После ввоза</t>
+          <t>4. Документы</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Подъёмники: ЭПСМ, регистрация в Гостехнадзоре, утильсбор. Бухучёт импорта.</t>
+          <t>Инвентарь под аренду = собственные нужды, не перепродажа: в контракте и заявке брокеру указать цель ввоза «для собственных нужд (сдача в аренду), не для реализации»; учитывать как своё имущество, а не товар. Если часть будет продаваться — заранее зарегистрироваться в «Честном знаке» (бесплатно, нужна ЭЦП).</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr"/>
@@ -9128,12 +9128,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>9. После ввоза</t>
+          <t>5. Контракт</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Вычет ввозного НДС (ст. 171 п. 2, 172 НК): в квартале, когда товар выпущен, принят к учёту и НДС уплачен (ДТ + платёжка на ЕЛС ФТС + отчёт о расходовании из ЛК участника ВЭД). Пример: выпуск в ноябре 2026 → декларация за IV кв. до 25.01.2027.</t>
+          <t>До заказа проверить налоговый режим: ОСНО или УСН с НДС 22% — ввозной НДС к вычету; УСН без НДС или с НДС 5%/7% — вычета нет, НДС идёт в стоимость (с 2026 г. НДС на УСН платят при доходе &gt; 20 млн ₽/год).</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr"/>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Инвентарь (МПЗ): вычет можно перенести в пределах 3 лет с даты принятия к учёту. Подъёмники (ОС): вычет после принятия к учёту, безопаснее — после ввода в эксплуатацию и целиком в одном квартале.</t>
+          <t>Подъёмники: ЭПСМ, регистрация в Гостехнадзоре, утильсбор. Бухучёт импорта.</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr"/>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Экологический сбор (ст. 24.5 ФЗ-89): за упаковку и за товары из перечня ПП РФ № 2414 от 29.12.2023 (в т. ч. текстиль, изделия из пластмасс, электрооборудование, АКБ). Вести учёт массы ввезённых товаров и упаковки по кодам ТН ВЭД и видам упаковки (картон, плёнка, пластик, дерево).</t>
+          <t>Вычет ввозного НДС (ст. 171 п. 2, 172 НК): в квартале, когда товар выпущен, принят к учёту и НДС уплачен (ДТ + платёжка на ЕЛС ФТС + отчёт о расходовании из ЛК участника ВЭД). Пример: выпуск в ноябре 2026 → декларация за IV кв. до 25.01.2027.</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr"/>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Экосбор: до 15 апреля следующего года — отчётность в Росприроднадзор (масса товаров и упаковки) и уплата сбора. Ставка = базовая ставка × коэффициент (ПП РФ № 1041 от 01.08.2024) × масса × норматив утилизации. Альтернатива — договор с утилизатором из реестра (закрыть норматив), иногда дешевле. Запросить у поставщика вес упаковки по видам.</t>
+          <t>Что ещё к вычету (при НДС 22%), кроме таможенного НДС: НДС в счетах-фактурах российских поставщиков — брокер, сертификация, доставка по РФ, склад. Международная перевозка — 0%, вычитать нечего; таможенный сбор и пошлина — без НДС. Китайский инвойс вычета не даёт.</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr"/>
@@ -9185,10 +9185,49 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
+          <t>Инвентарь (МПЗ): вычет можно перенести в пределах 3 лет с даты принятия к учёту. Подъёмники (ОС): вычет после принятия к учёту, безопаснее — после ввода в эксплуатацию и целиком в одном квартале.</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>9. После ввоза</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Экологический сбор (ст. 24.5 ФЗ-89): за упаковку и за товары из перечня ПП РФ № 2414 от 29.12.2023 (в т. ч. текстиль, изделия из пластмасс, электрооборудование, АКБ). Вести учёт массы ввезённых товаров и упаковки по кодам ТН ВЭД и видам упаковки (картон, плёнка, пластик, дерево).</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>9. После ввоза</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Экосбор: до 15 апреля следующего года — отчётность в Росприроднадзор (масса товаров и упаковки) и уплата сбора. Ставка = базовая ставка × коэффициент (ПП РФ № 1041 от 01.08.2024) × масса × норматив утилизации. Альтернатива — договор с утилизатором из реестра (закрыть норматив), иногда дешевле. Запросить у поставщика вес упаковки по видам.</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>9. После ввоза</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
           <t>Кассовый разрыв: если вычет больше НДС с аренды — возмещение после камеральной проверки (до 2 мес.). Деньги вернутся примерно через 3–5 месяцев после уплаты на таможне.</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr"/>
+      <c r="C37" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
+++ b/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Документы и риски" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Источники" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Экосбор" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Чек-лист до заказа" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Утиль и экосбор по кодам" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Чек-лист до заказа" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -123,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,6 +203,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8402,7 +8409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8746,16 +8753,1007 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Отчётность по экосбору в 2026 году — три формы (за 2026 год сдаются до 15.04.2027, импортёры — в центральный аппарат Росприроднадзора)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Форма</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Чем утверждена</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Кто сдаёт</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Откуда брать данные</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>1. Отчётность о массе товаров и упаковки</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>ПП РФ от 31.05.2024 № 741 (отдельная форма для импортёров из третьих стран)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Все импортёры товаров из перечня ПП № 2414 и товаров в упаковке — независимо от того, продаются товары или используются для своих нужд</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Масса товаров — вес нетто из ДТ; масса упаковки — вес брутто минус нетто из ДТ/упаковочного листа, разбивка по видам (картон, плёнка, дерево, пластик) — из спецификации поставщика или взвешиванием образцов</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2. Отчётность о выполнении нормативов утилизации</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>ПП РФ от 31.05.2024 № 742</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Только те, кто утилизировал сам или по договору с утилизатором из реестра (иначе не сдаётся)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Акты утилизации от утилизатора из реестра Росприроднадзора</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>3. Расчёт суммы экологического сбора</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>ПП РФ от 30.12.2024 № 1990 (приложение № 1)</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Все, у кого норматив не закрыт утилизацией полностью</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Масса из формы 1 × норматив (ПП № 2414) − утилизировано (форма 2) × ставка и коэффициент (ПП № 1041)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Штрафы</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>• Неуплата или неполная уплата экосбора в срок (ст. 8.41.1 КоАП): юрлица — 3-кратная неуплаченная сумма, но не менее 500 тыс. ₽; ИП — 3-кратная сумма, но не менее 250 тыс. ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>• Непредставление, несвоевременное представление, неполные или недостоверные сведения в отчётности (КоАП в ред. с 03.03.2026) — для юрлиц до 150 тыс. ₽; занижение массы упаковки = неполная уплата сбора → плюс штраф по ст. 8.41.1 и доначисление сбора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>• Росприроднадзор сверяет отчётность с данными ФТС по ДТ: расхождение массы с декларациями — типовой повод для требования и штрафа.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A26:I26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>За какие позиции платится утилизационный сбор и экологический сбор</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Утильсбор (ПП РФ № 81) — только транспорт и самоходные машины, платится ДО выпуска с таможни. Экосбор (ФЗ-89, ПП РФ № 2414 — перечень и нормативы) — за товар из перечня и за упаковку, платится за год до 15 апреля следующего года. Принадлежность к группе ПП № 2414 определяется по коду ОКПД2/ТН ВЭД в приложении — «проверить» = сверить до отчётности.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Код ТН ВЭД</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Позиции из заявок</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Утильсбор</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Экосбор за товар</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Норматив 2026</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Экосбор за упаковку</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>8716 80 000 0</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Тележка клининговая Vileda UltraSpeed Pro; Тележка клининговая Vileda UltraSpeed Mini; Тележка клининговая Vileda MicroBasic</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D5" s="38" t="inlineStr">
+        <is>
+          <t>Проверить (металл/пластмасса)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>3924 90 000 9</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Ведро с педальным отжимом Vileda EasyPress; Ведро двухсекционное Vileda Professional (грязная/чистая вода); Ведро трёхсекционное с ситом-отжимом; Пресс отжимной навесной на ведро</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Да, вероятно — изделия из пластмасс</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>35%?</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Норматив сверить с ПП № 2414 по группе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>6307 10 900 0</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Моп Vileda UltraSpeed Twist Mop (сменный, петлевой); Моп веревочный (шнуровой) из хлопка/вискозы; Салфетки вафельные (для полировки без разводов)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Да — текстильные изделия</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>6307 10 100 0</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Моп плоский Vileda MicroTech (флет-моп, микрофибра); Моп из микрофибры повышенной впитываемости (для больших разливов); Моп для сухой уборки (пыли) плоский, микрофибра; Моп для сухой уборки ворсистый (антистатический); Салфетки из микрофибры Vileda MicroFit — красный 40х40; Салфетки из микрофибры Vileda MicroFit — синий 40х40; Салфетки из микрофибры Vileda MicroFit — жёлтый 40х40; Салфетки из микрофибры Vileda MicroFit — зелёный 40х40; Салфетки из микрофибры Vileda MicroFit — белый 40х40; Салфетки Vileda MicroTech Pro (для оргтехники/стёкол); Моп широкий промышленный (увеличенная площадь захвата); Салфетки из микрофибры Vileda MicroFit — красный 70х80; Салфетки из микрофибры Vileda MicroFit — синий 70х80; Салфетки из микрофибры Vileda MicroFit — жёлтый 70х80; Салфетки из микрофибры Vileda MicroFit — зелёный 70х80; Предварительно пропитанные салфетки (prewetted system); Моп из микрофибры, разрешённый для контакта с пищ. поверхностями</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Да — текстильные изделия</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>9603 90 910 0</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Моп-твист (спин-моп) с ручным отжимом; Моп-щётка для сбора крупного мусора; Щётка Vileda Professional (жёсткая/универсальная); Щётка мягкая для деликатных поверхностей; Щётка угловая (для труднодоступных мест); Ёршики/щётки для труб и стоков; Насадки-щётки на удлинителях; Телескопическая штанга с водоподачей (Water-Fed Pole)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Да — «Мётлы и щётки для домашней уборки» есть в перечне</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>3926 90 970 9</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Держатель для плоского мопа (флет-моп), быстросъёмный; Держатель для петлевого/веревочного мопа; Таблички информационные «Мокрый пол»</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Да, вероятно — изделия из пластмасс</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>35%?</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7616 99 900 8</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Ручка телескопическая алюминиевая; Ручка телескопическая для высоких потолков/стеллажей (удлинённая); Стремянка-платформа</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D11" s="38" t="inlineStr">
+        <is>
+          <t>Проверить</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>9603 90 990 0</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Сгон для воды на пол (водосгон), резиновый, широкий; Сгон для воды на пол, узкий (для труднодоступных зон/углов); Сгон для стёкол (склиз) с мягкой резинкой; Сгон комбинированный (стекло + пол, двусторонний); Сгон для воды широкий промышленный (от 60 см); Сгон для воды пищевого класса (для цехов)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Да, вероятно — группа щёток/мётел</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Сгоны профессиональные — сверить группу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>4016 99 970 8</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Запасные резинки/лезвия для сгонов</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Да, вероятно — изделия из резины</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>8205 59 809 9</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Скребок для пола с металлическим лезвием (снятие наклеек/жвачки); Скребок для стёкол Vileda UltraSpeed Glass</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="inlineStr">
+        <is>
+          <t>Проверить (инструмент ручной)</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>8509 80 000 0</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Оконная система Vileda Windomatic (моп + сгон)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Да — электробытовые приборы + отдельно Li-ion АКБ</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>АКБ — своя группа и норматив.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>5603 14 900 0</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Абсорбирующие салфетки/маты для разливов (масла, ГСМ)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Да, вероятно — нетканые текстильные материалы</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>30%?</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>8505 19 900 0</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Магнитная щётка-подметалка (сбор металлической стружки)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D17" s="38" t="inlineStr">
+        <is>
+          <t>Проверить</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>6307 10 300 0</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Одноразовые салфетки/мопы (снижение риска перекрёстного заражения); Моп одноразовый для дезинфекции процедурных</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Да — текстильные изделия</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>8427 10 100 0</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Шарнирная электровышка (Articulated Boom); Телескопическая электровышка (Telescopic Boom); Паук-подъёмник (Spider Lift, гусеничный)</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>ПРОВЕРИТЬ до контракта (ПП № 81, самоходные машины): база 172 500 ₽ × коэффициент</t>
+        </is>
+      </c>
+      <c r="D19" s="38" t="inlineStr">
+        <is>
+          <t>Проверить + тяговые АКБ — да</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Если утильсбор применим — платится до выпуска и может превысить пошлину (0%). Сверить по модели у брокера.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>7610 90 900 0</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Вышка-тура алюминиевая передвижная</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D20" s="38" t="inlineStr">
+        <is>
+          <t>Проверить (металлоконструкции)</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>8508 19 000 9</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Промышленный пылесос (класс L/M/H)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Да — электрооборудование</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>8424 30 100 0</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Аппарат сухой чистки сжатым воздухом</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Да, вероятно — оборудование с электроприводом</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>8424 30 080 0</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Аппарат высокого/низкого давления с пеногенератором</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Да, вероятно — оборудование с электроприводом</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>8508 19 000 1</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Промышленный пылесос-влаговсос</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Да — электрооборудование</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>3402 90 900 0</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Химия: обезжириватели, антикоррозийные составы</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Да — моющие средства; тара от химии — как упаковка</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>8544 42 900 9</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Удлинители промышленные на катушках</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Да — провода и кабели</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>8502 11 200 0</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Подключение к сети цеха / генератор</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Да, вероятно — генераторы</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>8467 21 100 0</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Аккумуляторные инструменты</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Да — электроинструмент + отдельно Li-ion АКБ</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>по ПП 2414</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Да — вся упаковка (коробки, плёнка, паллеты), норматив 75%</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
+++ b/import-china/ТНВЭД_импорт_Китай_расчет.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Vileda — инвентарь" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Оборудование (высота)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Параметры" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Документы и риски" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Источники" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Экосбор" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Утиль и экосбор по кодам" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Чек-лист до заказа" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vileda — инвентарь" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование (высота)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Документы и риски" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Экосбор" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Утиль и экосбор по кодам" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Чек-лист до заказа" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -186,6 +186,7 @@
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1148,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U85"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5993,10 +5994,34 @@
         <v/>
       </c>
     </row>
+    <row r="86">
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>Расходы на платёж поставщику (банк, посредник, конвертация), ₽</t>
+        </is>
+      </c>
+      <c r="D86" s="19">
+        <f>D74*Параметры!$B$4*Параметры!$B$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>ИТОГО себестоимость партии с расходами на платёж, ₽</t>
+        </is>
+      </c>
+      <c r="D87" s="20">
+        <f>D85+D86</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="B74:C74"/>
     <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B86:C86"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B80:C80"/>
     <mergeCell ref="B81:C81"/>
@@ -6020,7 +6045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7809,8 +7834,31 @@
         <v/>
       </c>
     </row>
+    <row r="39">
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>Расходы на платёж поставщику (банк, посредник, конвертация), ₽</t>
+        </is>
+      </c>
+      <c r="D39" s="19">
+        <f>D27*Параметры!$B$4*Параметры!$B$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>ИТОГО себестоимость партии с расходами на платёж, ₽</t>
+        </is>
+      </c>
+      <c r="D40" s="20">
+        <f>D38+D39</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B29:C29"/>
@@ -7821,6 +7869,7 @@
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="A3:L3"/>
     <mergeCell ref="B35:C35"/>
@@ -8114,6 +8163,21 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Расходы на платёж поставщику (банк, посредник, конвертация), % к инвойсу</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ФАКТ платежа 05.06.2026 (ИП Рожков, 115 243 CNY): курс банка 11,20 против ЦБ 10,9536 (+2,25%), комиссия третьего банка 4,50%, перевод 0,30%, агент валютного контроля 0,16%. Итого 7,21% к инвойсу по курсу ЦБ. В таможенную стоимость не входит.</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
@@ -8182,7 +8246,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Лицензии</t>
         </is>
@@ -8194,7 +8258,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>Сертификаты — итог</t>
         </is>
@@ -8206,7 +8270,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>Товарный знак Vileda</t>
         </is>
@@ -8218,7 +8282,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>Санкции</t>
         </is>
@@ -8230,7 +8294,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>Самоходная техника</t>
         </is>
@@ -8242,7 +8306,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Преференции</t>
         </is>
@@ -8254,7 +8318,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>НДС</t>
         </is>
@@ -8266,7 +8330,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Таможенная стоимость</t>
         </is>
@@ -8278,7 +8342,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Валютный контроль</t>
         </is>
@@ -8290,7 +8354,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Спорные коды</t>
         </is>
@@ -8302,7 +8366,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Специфические пошлины</t>
         </is>
@@ -8314,7 +8378,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>Опасные грузы</t>
         </is>
@@ -8350,49 +8414,49 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>1. Коды подобраны по текстам позиций ТН ВЭД ЕАЭС и Пояснениям к ТН ВЭД по описанию товаров из заявок, без спецификаций и фото. Окончательный код в ДТ определяет декларант (брокер).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>2. Ставки пошлин — ЕТТ ЕАЭС (Решение Совета ЕЭК № 80 от 14.09.2021 в действ. ред.) по данным открытых справочников (Альта-Софт, IFCG, TKS, kodtnved.ru), сверены через поиск в сентябре 2026. Прямой доступ к базам из среды расчёта был закрыт — перед подачей ДТ сверьте каждую ставку.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>3. НДС 22% — Федеральный закон № 425-ФЗ (с 01.01.2026).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>4. Таможенные сборы — ПП РФ от 28.11.2024 № 1637 (ставки с 01.01.2026).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>5. Техрегламенты: ТР ТС 004/2011 (низковольтное оборудование), 010/2011 (машины и оборудование), 012/2011 (взрывозащита), 017/2011 (лёгкая промышленность), 020/2011 (ЭМС), ТР ЕАЭС 037/2016 (RoHS), ТР ЕАЭС 041/2017 (химическая продукция).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>6. Стоимость брокера и сертификации — рыночные оценки, не прайс конкретного исполнителя.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>7. Курсы валют в «Параметрах» — заглушки, подставьте курс ЦБ РФ.</t>
         </is>
@@ -8492,7 +8556,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>Упаковка — бумага и картон</t>
         </is>
@@ -8502,13 +8566,13 @@
           <t>Гофрокороба, картонные вкладыши, бумажные этикетки</t>
         </is>
       </c>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="34" t="n">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="35" t="n">
         <v>0.75</v>
       </c>
-      <c r="E6" s="33" t="n"/>
+      <c r="E6" s="34" t="n"/>
       <c r="F6" s="23" t="n"/>
-      <c r="G6" s="35" t="n">
+      <c r="G6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="13">
@@ -8522,7 +8586,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>Упаковка — полимерная</t>
         </is>
@@ -8532,13 +8596,13 @@
           <t>Плёнка, пакеты, стрейч, пузырчатая плёнка, пластиковые вкладыши</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="34" t="n">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="35" t="n">
         <v>0.75</v>
       </c>
-      <c r="E7" s="33" t="n"/>
+      <c r="E7" s="34" t="n"/>
       <c r="F7" s="23" t="n"/>
-      <c r="G7" s="35" t="n">
+      <c r="G7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="13">
@@ -8548,7 +8612,7 @@
       <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Упаковка — деревянная</t>
         </is>
@@ -8558,13 +8622,13 @@
           <t>Паллеты, обрешётка (если остаются у вас)</t>
         </is>
       </c>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="34" t="n">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="35" t="n">
         <v>0.75</v>
       </c>
-      <c r="E8" s="33" t="n"/>
+      <c r="E8" s="34" t="n"/>
       <c r="F8" s="23" t="n"/>
-      <c r="G8" s="35" t="n">
+      <c r="G8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="13">
@@ -8578,7 +8642,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Товары — текстиль</t>
         </is>
@@ -8588,13 +8652,13 @@
           <t>Мопы, салфетки, тряпки (6307)</t>
         </is>
       </c>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="34" t="n">
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="35" t="n">
         <v>0.3</v>
       </c>
-      <c r="E9" s="33" t="n"/>
+      <c r="E9" s="34" t="n"/>
       <c r="F9" s="23" t="n"/>
-      <c r="G9" s="35" t="n">
+      <c r="G9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="13">
@@ -8608,7 +8672,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Товары — изделия из пластмасс</t>
         </is>
@@ -8618,13 +8682,13 @@
           <t>Вёдра, прессы, держатели, таблички (3924, 3926)</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="34" t="n">
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="35" t="n">
         <v>0.35</v>
       </c>
-      <c r="E10" s="33" t="n"/>
+      <c r="E10" s="34" t="n"/>
       <c r="F10" s="23" t="n"/>
-      <c r="G10" s="35" t="n">
+      <c r="G10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="13">
@@ -8638,7 +8702,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Товары — электрооборудование</t>
         </is>
@@ -8648,11 +8712,11 @@
           <t>Пылесосы, мойки, аппараты, удлинители, инструмент, Windomatic</t>
         </is>
       </c>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="34" t="n"/>
-      <c r="E11" s="33" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="34" t="n"/>
       <c r="F11" s="23" t="n"/>
-      <c r="G11" s="35" t="n">
+      <c r="G11" s="36" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="13">
@@ -8666,7 +8730,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Товары — аккумуляторы</t>
         </is>
@@ -8676,11 +8740,11 @@
           <t>Li-ion АКБ инструмента, Windomatic, тяговые АКБ подъёмников</t>
         </is>
       </c>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="33" t="n"/>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="34" t="n"/>
       <c r="F12" s="23" t="n"/>
-      <c r="G12" s="35" t="n">
+      <c r="G12" s="36" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="13">
@@ -8694,7 +8758,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Товары — химия</t>
         </is>
@@ -8704,11 +8768,11 @@
           <t>Моющие средства и тара от них (3402)</t>
         </is>
       </c>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="34" t="n"/>
-      <c r="E13" s="33" t="n"/>
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="34" t="n"/>
       <c r="F13" s="23" t="n"/>
-      <c r="G13" s="35" t="n">
+      <c r="G13" s="36" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="13">
@@ -8722,22 +8786,22 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>ИТОГО экосбор за год, ₽</t>
         </is>
       </c>
-      <c r="B14" s="37" t="n"/>
-      <c r="C14" s="37" t="n"/>
-      <c r="D14" s="37" t="n"/>
-      <c r="E14" s="37" t="n"/>
-      <c r="F14" s="37" t="n"/>
-      <c r="G14" s="37" t="n"/>
+      <c r="B14" s="38" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="38" t="n"/>
       <c r="H14" s="20">
         <f>SUM(H6:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="37" t="n"/>
+      <c r="I14" s="38" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -8856,21 +8920,21 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t>• Неуплата или неполная уплата экосбора в срок (ст. 8.41.1 КоАП): юрлица — 3-кратная неуплаченная сумма, но не менее 500 тыс. ₽; ИП — 3-кратная сумма, но не менее 250 тыс. ₽.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>• Непредставление, несвоевременное представление, неполные или недостоверные сведения в отчётности (КоАП в ред. с 03.03.2026) — для юрлиц до 150 тыс. ₽; занижение массы упаковки = неполная уплата сбора → плюс штраф по ст. 8.41.1 и доначисление сбора.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>• Росприроднадзор сверяет отчётность с данными ФТС по ДТ: расхождение массы с декларациями — типовой повод для требования и штрафа.</t>
         </is>
@@ -8973,7 +9037,7 @@
           <t>Нет</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="39" t="inlineStr">
         <is>
           <t>Проверить (металл/пластмасса)</t>
         </is>
@@ -9171,7 +9235,7 @@
           <t>Нет</t>
         </is>
       </c>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="39" t="inlineStr">
         <is>
           <t>Проверить</t>
         </is>
@@ -9270,7 +9334,7 @@
           <t>Нет</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D14" s="39" t="inlineStr">
         <is>
           <t>Проверить (инструмент ручной)</t>
         </is>
@@ -9369,7 +9433,7 @@
           <t>Нет</t>
         </is>
       </c>
-      <c r="D17" s="38" t="inlineStr">
+      <c r="D17" s="39" t="inlineStr">
         <is>
           <t>Проверить</t>
         </is>
@@ -9426,12 +9490,12 @@
           <t>Шарнирная электровышка (Articulated Boom); Телескопическая электровышка (Telescopic Boom); Паук-подъёмник (Spider Lift, гусеничный)</t>
         </is>
       </c>
-      <c r="C19" s="39" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>ПРОВЕРИТЬ до контракта (ПП № 81, самоходные машины): база 172 500 ₽ × коэффициент</t>
         </is>
       </c>
-      <c r="D19" s="38" t="inlineStr">
+      <c r="D19" s="39" t="inlineStr">
         <is>
           <t>Проверить + тяговые АКБ — да</t>
         </is>
@@ -9468,7 +9532,7 @@
           <t>Нет</t>
         </is>
       </c>
-      <c r="D20" s="38" t="inlineStr">
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>Проверить (металлоконструкции)</t>
         </is>
